--- a/stories/arbres/TREE-FAM-004.xlsx
+++ b/stories/arbres/TREE-FAM-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est à la maison, avec maman. Papa est dans le jardin. Un bocal est trop lourd. Tom n'y arrive pas. Maman dit : on peut aller vers eux. On va dire le besoin. On appelle papa ou maman.</t>
+          <t>Tom est à la maison, avec maman. Papa est dans le jardin. Un bocal est trop lourd. Tom n'y arrive pas. On peut aller vers eux. On va dire le besoin. On appelle papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est à la maison, avec maman. Papa est dans le jardin. Un bocal est trop lourd. Tom n'y arrive pas.
+maman|On peut aller vers eux. On va dire le besoin. On appelle papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1645,6 +1673,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat de la maison miaule. Tom veut le panier. C'est trop difficile. Il va vers maman. Il dit le besoin : j'ai besoin d'aide. On va vers eux. On dit le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1821,6 +1854,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On appelle papa ou maman ?</t>
         </is>
       </c>
     </row>
@@ -1989,6 +2027,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom respire. Maman est là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2175,6 +2218,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2337,6 +2385,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Tom va vers le bac à sable. C'est trop loin tout seul. Il va vers maman. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2525,6 +2578,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le chat. Puis le bac à sable. Puis rouge. Un ballon s'immobilise. Tom raccroche un linge. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Tom répète tout bas le geste. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de le chat. Et de le bac à sable. Et de vert. Un vélo passe au loin. Tom marche près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3523,7 +3611,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Plus tard, Tom va vers le toboggan. La marche est haute. Il va vers maman. Il dit le besoin. Maman dit : je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+          <t>Plus tard, Tom va vers le toboggan. La marche est haute. Il va vers maman. Il dit le besoin. Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3661,6 +3749,12 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Tom va vers le toboggan. La marche est haute. Il va vers maman. Il dit le besoin.
+maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3849,6 +3943,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4013,6 +4112,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de le chat. Tom s'arrête. Un linge sèche à l'air. Tom plie un pull. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4199,7 +4308,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tom range le toboggan. bleu reste près de le chat. Le savon sent bon. Tom dit : j'ai appris. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+          <t>Tom range le toboggan. bleu reste près de le chat. Le savon sent bon. J'ai appris. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4337,6 +4446,13 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le toboggan. bleu reste près de le chat. Le savon sent bon.
+enfant-m|J'ai appris. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin.
+narrateur|Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4615,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4644,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. le chat reste dans le souvenir. Un ruban reste dans la poche. Tom chuchote : c'est fini. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. le chat reste dans le souvenir. Un ruban reste dans la poche. Tom chuchote : c'est fini. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4782,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. le chat reste dans le souvenir. Un ruban reste dans la poche. Tom chuchote : c'est fini. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4949,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5116,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Plus tard, Tom va vers les balançoires. Il n'arrive pas. Il va vers maman. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5173,6 +5309,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5337,6 +5478,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint rouge. les balançoires est rangé. le chat est fini. Il y a des miettes sur la table. Tom prend la main de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5645,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5812,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Tom pose les balançoires. le chat est derrière. On attend son tour. Tom dit merci à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5979,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6146,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre vert. Maman a vu le chat. Et les balançoires. Une cloche tinte, tout loin. Tom ferme le sac. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6313,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6476,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien des voisins aboie, tout loin. Tom veut fermer la porte. C'est trop difficile. Il appelle papa. Il va vers eux. Il dit le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6657,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On va vers eux, et on dit le besoin ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6830,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom retient le geste. Maman sourit. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7021,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6859,7 +7050,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Papa l'emmène au bac à sable. Tom veut le seau. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman dit : je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+          <t>Papa l'emmène au bac à sable. Tom veut le seau. C'est trop difficile. Il va vers eux. Il dit le besoin. Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -6997,6 +7188,12 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Papa l'emmène au bac à sable. Tom veut le seau. C'est trop difficile. Il va vers eux. Il dit le besoin.
+maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7185,6 +7382,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7349,6 +7551,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le chien. Puis le bac à sable. Puis rouge. Un crochet tient bien le manteau. Tom range la tasse. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7718,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7885,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. On dit merci. Tom range encore un peu, près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8052,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8219,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de le chien. Et de le bac à sable. Et de vert. Ça sent le pain chaud. Tom boit une gorgée d'eau. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8386,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8553,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Papa l'emmène au toboggan. Tom veut monter. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8509,6 +8746,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8673,6 +8915,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de le chien. Tom s'arrête. Une feuille tombe. Papa n'est pas loin. Tom les rejoint. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9082,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9249,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le toboggan. bleu reste près de le chien. On souffle doucement. Tom tend bleu à papa. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9416,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9445,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. le chien reste dans le souvenir. On écoute jusqu'au bout. Tom s'assoit près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. le chien reste dans le souvenir. On écoute jusqu'au bout. Tom s'assoit près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9583,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. le chien reste dans le souvenir. On écoute jusqu'au bout. Tom s'assoit près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9750,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9917,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Papa l'emmène aux balançoires. Tom veut s'asseoir. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9833,6 +10110,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -9997,6 +10279,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint rouge. les balançoires est rangé. le chien est fini. Le sol est un peu froid. Tom montre rouge à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10159,6 +10446,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10321,6 +10613,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Tom pose les balançoires. le chien est derrière. L'eau coule, tout petit bruit. Tom pose sa tête un moment. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10483,6 +10780,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10645,6 +10947,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre vert. Maman a vu le chien. Et les balançoires. Un chat miaule une fois. Tom pose les balançoires à sa place. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10807,6 +11114,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11277,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Une poule en peluche est coincée. Tom n'y arrive pas. Il va vers maman. Il dit le besoin. Maman vient. On appelle papa ou maman. On dit le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|C'est trop difficile. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom hoche la tête. On continue, avec maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11822,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11989,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maman l'emmène au bac. Tom veut un moule. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11845,6 +12182,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12009,6 +12351,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la poule. Puis le bac à sable. Puis rouge. On rit un peu. Tom serre la main de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12518,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12685,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. On range un objet. Tom sourit. Maman sourit aussi. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12852,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13019,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom se souvient de la poule. Et de le bac à sable. Et de vert. Le vent est doux. Tom ferme la porte, tout doux. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13186,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13353,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maman l'emmène au toboggan. Tom veut de l'aide. Il va vers eux. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13169,6 +13546,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13333,6 +13715,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le toboggan. Près de la poule. Tom s'arrête. Un galet est encore chaud. Tom caresse le doudou. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13882,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14049,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom range le toboggan. bleu reste près de la poule. La couverture est douce. Tom écoute maman encore une fois. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14216,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13843,7 +14245,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le toboggan aussi. la poule reste dans le souvenir. Une chaussette est encore sablée. Tom essuie ses mains. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+          <t>Vert est là. le toboggan aussi. la poule reste dans le souvenir. Une chaussette est encore sablée. Tom essuie ses mains. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13981,6 +14383,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le toboggan aussi. la poule reste dans le souvenir. Une chaussette est encore sablée. Tom essuie ses mains. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14550,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14167,7 +14579,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Maman l'emmène aux balançoires. Tom veut de l'aide. Il va vers eux. Il dit le besoin. Maman dit : je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+          <t>Maman l'emmène aux balançoires. Tom veut de l'aide. Il va vers eux. Il dit le besoin. Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14305,6 +14717,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maman l'emmène aux balançoires. Tom veut de l'aide. Il va vers eux. Il dit le besoin.
+maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14493,6 +14911,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14657,6 +15080,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint rouge. les balançoires est rangé. la poule est fini. Une tasse cliquette. Tom enfile ses chaussons. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14819,6 +15247,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14981,6 +15414,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Tom pose les balançoires. la poule est derrière. Un panier est posé sur le banc. Tom range la poule dans sa tête, comme un souvenir. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15143,6 +15581,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15305,6 +15748,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom montre vert. Maman a vu la poule. Et les balançoires. On entend un oiseau. Tom souffle, puis sourit à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15467,6 +15915,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15485,7 +15938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15558,6 +16011,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-004.xlsx
+++ b/stories/arbres/TREE-FAM-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On peut aller vers eux. On va dire le besoin. On appelle papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1513,6 +1519,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1678,6 +1689,7 @@
           <t>narrateur|Le chat de la maison miaule. Tom veut le panier. C'est trop difficile. Il va vers maman. Il dit le besoin : j'ai besoin d'aide. On va vers eux. On dit le besoin.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1861,6 +1873,7 @@
           <t>narrateur|On appelle papa ou maman ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2032,6 +2045,7 @@
           <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom respire. Maman est là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2223,6 +2237,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2390,6 +2405,7 @@
           <t>narrateur|Plus tard, Tom va vers le bac à sable. C'est trop loin tout seul. Il va vers maman. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2601,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2769,7 @@
           <t>narrateur|Tom a choisi le chat. Puis le bac à sable. Puis rouge. Un ballon s'immobilise. Tom raccroche un linge. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3105,7 @@
           <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. Une pomme brille un peu. Tom répète tout bas le geste. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3441,7 @@
           <t>narrateur|Tom se souvient de le chat. Et de le bac à sable. Et de vert. Un vélo passe au loin. Tom marche près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3778,7 @@
 maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3974,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4142,7 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de le chat. Tom s'arrête. Un linge sèche à l'air. Tom plie un pull. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4480,7 @@
 narrateur|Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4648,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4816,7 @@
           <t>narrateur|Vert est là. le toboggan aussi. le chat reste dans le souvenir. Un ruban reste dans la poche. Tom chuchote : c'est fini. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5152,7 @@
           <t>narrateur|Plus tard, Tom va vers les balançoires. Il n'arrive pas. Il va vers maman. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5348,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5483,6 +5516,7 @@
           <t>narrateur|Tom rejoint rouge. les balançoires est rangé. le chat est fini. Il y a des miettes sur la table. Tom prend la main de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5650,6 +5684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5817,6 +5852,7 @@
           <t>narrateur|Près de bleu. Tom pose les balançoires. le chat est derrière. On attend son tour. Tom dit merci à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5984,6 +6020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6151,6 +6188,7 @@
           <t>narrateur|Tom montre vert. Maman a vu le chat. Et les balançoires. Une cloche tinte, tout loin. Tom ferme le sac. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6318,6 +6356,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6520,11 @@
           <t>narrateur|Le chien des voisins aboie, tout loin. Tom veut fermer la porte. C'est trop difficile. Il appelle papa. Il va vers eux. Il dit le besoin.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6664,6 +6708,7 @@
           <t>narrateur|On va vers eux, et on dit le besoin ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6835,6 +6880,7 @@
           <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom retient le geste. Maman sourit. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7026,6 +7072,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7194,6 +7241,7 @@
 maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7389,6 +7437,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7556,6 +7605,11 @@
           <t>narrateur|Tom a choisi le chien. Puis le bac à sable. Puis rouge. Un crochet tient bien le manteau. Tom range la tasse. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7723,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7945,7 @@
           <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. On dit merci. Tom range encore un peu, près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8113,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8281,11 @@
           <t>narrateur|Tom se souvient de le chien. Et de le bac à sable. Et de vert. Ça sent le pain chaud. Tom boit une gorgée d'eau. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8453,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8621,7 @@
           <t>narrateur|Papa l'emmène au toboggan. Tom veut monter. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8817,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8985,11 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de le chien. Tom s'arrête. Une feuille tombe. Papa n'est pas loin. Tom les rejoint. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9157,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9325,11 @@
           <t>narrateur|Tom range le toboggan. bleu reste près de le chien. On souffle doucement. Tom tend bleu à papa. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9497,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9665,11 @@
           <t>narrateur|Vert est là. le toboggan aussi. le chien reste dans le souvenir. On écoute jusqu'au bout. Tom s'assoit près de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9837,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +10005,7 @@
           <t>narrateur|Papa l'emmène aux balançoires. Tom veut s'asseoir. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10117,6 +10201,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10284,6 +10369,11 @@
           <t>narrateur|Tom rejoint rouge. les balançoires est rangé. le chien est fini. Le sol est un peu froid. Tom montre rouge à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10451,6 +10541,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10618,6 +10709,11 @@
           <t>narrateur|Près de bleu. Tom pose les balançoires. le chien est derrière. L'eau coule, tout petit bruit. Tom pose sa tête un moment. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10785,6 +10881,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10952,6 +11049,11 @@
           <t>narrateur|Tom montre vert. Maman a vu le chien. Et les balançoires. Un chat miaule une fois. Tom pose les balançoires à sa place. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11119,6 +11221,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11385,7 @@
           <t>narrateur|Une poule en peluche est coincée. Tom n'y arrive pas. Il va vers maman. Il dit le besoin. Maman vient. On appelle papa ou maman. On dit le besoin.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11569,7 @@
           <t>narrateur|C'est trop difficile. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11741,7 @@
           <t>narrateur|Oui. On peut aller vers eux. On va dire le besoin. Tom hoche la tête. On continue, avec maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11827,6 +11933,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11994,6 +12101,7 @@
           <t>narrateur|Maman l'emmène au bac. Tom veut un moule. C'est trop difficile. Il va vers eux. Il dit le besoin. Maman reste tout près. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12189,6 +12297,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12356,6 +12465,7 @@
           <t>narrateur|Tom a choisi la poule. Puis le bac à sable. Puis rouge. On rit un peu. Tom serre la main de maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12523,6 +12633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12690,6 +12801,7 @@
           <t>narrateur|Tom s'arrête près de bleu. le bac à sable est rangé. On range un objet. Tom sourit. Maman sourit aussi. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12857,6 +12969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13024,6 +13137,7 @@
           <t>narrateur|Tom se souvient de la poule. Et de le bac à sable. Et de vert. Le vent est doux. Tom ferme la porte, tout doux. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13191,6 +13305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13358,6 +13473,7 @@
           <t>narrateur|Maman l'emmène au toboggan. Tom veut de l'aide. Il va vers eux. Il dit le besoin. Maman montre le geste, lentement. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13553,6 +13669,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13720,6 +13837,7 @@
           <t>narrateur|Avec rouge. Après le toboggan. Près de la poule. Tom s'arrête. Un galet est encore chaud. Tom caresse le doudou. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13887,6 +14005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14054,6 +14173,7 @@
           <t>narrateur|Tom range le toboggan. bleu reste près de la poule. La couverture est douce. Tom écoute maman encore une fois. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14221,6 +14341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14388,6 +14509,7 @@
           <t>narrateur|Vert est là. le toboggan aussi. la poule reste dans le souvenir. Une chaussette est encore sablée. Tom essuie ses mains. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14555,6 +14677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14723,6 +14846,7 @@
 maman|Je suis là. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14918,6 +15042,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15085,6 +15210,7 @@
           <t>narrateur|Tom rejoint rouge. les balançoires est rangé. la poule est fini. Une tasse cliquette. Tom enfile ses chaussons. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15252,6 +15378,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15419,6 +15546,7 @@
           <t>narrateur|Près de bleu. Tom pose les balançoires. la poule est derrière. Un panier est posé sur le banc. Tom range la poule dans sa tête, comme un souvenir. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15586,6 +15714,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15753,6 +15882,7 @@
           <t>narrateur|Tom montre vert. Maman a vu la poule. Et les balançoires. On entend un oiseau. Tom souffle, puis sourit à maman. Quand c'est trop difficile, on peut aller vers eux. On va dire le besoin. On appelle papa ou maman. On peut aller vers eux. On va dire le besoin. Tom dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15920,6 +16050,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15938,7 +16069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16018,6 +16149,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16219,6 +16364,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
